--- a/slab_month_product.xlsx
+++ b/slab_month_product.xlsx
@@ -606,16 +606,16 @@
         <v>42</v>
       </c>
       <c r="D2">
-        <v>528</v>
+        <v>615</v>
       </c>
       <c r="E2">
-        <v>531</v>
+        <v>619</v>
       </c>
       <c r="F2">
-        <v>531</v>
+        <v>619</v>
       </c>
       <c r="G2">
-        <v>3207.24</v>
+        <v>3738.76</v>
       </c>
       <c r="H2">
         <v>58</v>
@@ -633,10 +633,10 @@
         <v>0.98</v>
       </c>
       <c r="M2">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="N2">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="O2">
         <v>0.02</v>
@@ -653,16 +653,16 @@
         <v>42</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>36.24</v>
+        <v>66.44</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -697,16 +697,16 @@
         <v>42</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="E4">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="G4">
-        <v>138.92</v>
+        <v>235.56</v>
       </c>
       <c r="H4">
         <v>4</v>
@@ -724,7 +724,7 @@
         <v>0</v>
       </c>
       <c r="M4">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -744,16 +744,16 @@
         <v>42</v>
       </c>
       <c r="D5">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="E5">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="F5">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="G5">
-        <v>326.16</v>
+        <v>446.96</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -771,7 +771,7 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -791,16 +791,16 @@
         <v>42</v>
       </c>
       <c r="D6">
-        <v>233</v>
+        <v>264</v>
       </c>
       <c r="E6">
-        <v>234</v>
+        <v>265</v>
       </c>
       <c r="F6">
-        <v>234</v>
+        <v>265</v>
       </c>
       <c r="G6">
-        <v>1413.36</v>
+        <v>1600.6</v>
       </c>
       <c r="H6">
         <v>24</v>
@@ -818,10 +818,10 @@
         <v>0.6</v>
       </c>
       <c r="M6">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="N6">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="O6">
         <v>0.01</v>
@@ -838,16 +838,16 @@
         <v>42</v>
       </c>
       <c r="D7">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E7">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="F7">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G7">
-        <v>736.88</v>
+        <v>767.08</v>
       </c>
       <c r="H7">
         <v>16</v>
@@ -868,7 +868,7 @@
         <v>0.13</v>
       </c>
       <c r="N7">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="O7">
         <v>0.02</v>
@@ -885,16 +885,16 @@
         <v>42</v>
       </c>
       <c r="D8">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E8">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F8">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G8">
-        <v>344.28</v>
+        <v>362.4</v>
       </c>
       <c r="H8">
         <v>5</v>
@@ -912,10 +912,10 @@
         <v>5.7</v>
       </c>
       <c r="M8">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="N8">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="O8">
         <v>0.08</v>
@@ -979,16 +979,16 @@
         <v>42</v>
       </c>
       <c r="D10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G10">
-        <v>60.4</v>
+        <v>66.44</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1023,16 +1023,16 @@
         <v>42</v>
       </c>
       <c r="D11">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E11">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F11">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G11">
-        <v>48.32</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -1050,7 +1050,7 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -3867,16 +3867,16 @@
         <v>42</v>
       </c>
       <c r="D74">
-        <v>666</v>
+        <v>725</v>
       </c>
       <c r="E74">
-        <v>743</v>
+        <v>804</v>
       </c>
       <c r="F74">
-        <v>748</v>
+        <v>809</v>
       </c>
       <c r="G74">
-        <v>4811</v>
+        <v>5158.09</v>
       </c>
       <c r="H74">
         <v>1242</v>
@@ -3894,13 +3894,13 @@
         <v>9.52</v>
       </c>
       <c r="M74">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="N74">
-        <v>15.92</v>
+        <v>14.71</v>
       </c>
       <c r="O74">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="75" spans="1:15">
@@ -4619,16 +4619,16 @@
         <v>42</v>
       </c>
       <c r="D90">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E90">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F90">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G90">
-        <v>142.34</v>
+        <v>170.79</v>
       </c>
       <c r="H90">
         <v>124</v>
@@ -4646,13 +4646,13 @@
         <v>0.99</v>
       </c>
       <c r="M90">
-        <v>5.17</v>
+        <v>4.28</v>
       </c>
       <c r="N90">
-        <v>5.12</v>
+        <v>4.24</v>
       </c>
       <c r="O90">
-        <v>0.86</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="91" spans="1:15">
@@ -5371,16 +5371,16 @@
         <v>42</v>
       </c>
       <c r="D106">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="E106">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="F106">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="G106">
-        <v>601.15</v>
+        <v>652.36</v>
       </c>
       <c r="H106">
         <v>99</v>
@@ -5398,13 +5398,13 @@
         <v>2.03</v>
       </c>
       <c r="M106">
-        <v>1.03</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N106">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="O106">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="107" spans="1:15">
@@ -6123,16 +6123,16 @@
         <v>42</v>
       </c>
       <c r="D122">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E122">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="F122">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="G122">
-        <v>983.37</v>
+        <v>1023.2</v>
       </c>
       <c r="H122">
         <v>162</v>
@@ -6150,13 +6150,13 @@
         <v>1.86</v>
       </c>
       <c r="M122">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="N122">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="O122">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="123" spans="1:15">
@@ -6875,16 +6875,16 @@
         <v>42</v>
       </c>
       <c r="D138">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E138">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F138">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G138">
-        <v>1417.16</v>
+        <v>1434.23</v>
       </c>
       <c r="H138">
         <v>442</v>
@@ -6902,13 +6902,13 @@
         <v>5.8</v>
       </c>
       <c r="M138">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="N138">
-        <v>12.16</v>
+        <v>11.99</v>
       </c>
       <c r="O138">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="139" spans="1:15">
@@ -7627,16 +7627,16 @@
         <v>42</v>
       </c>
       <c r="D154">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E154">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F154">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G154">
-        <v>210.98</v>
+        <v>228.05</v>
       </c>
       <c r="H154">
         <v>123</v>
@@ -7654,13 +7654,13 @@
         <v>24.65</v>
       </c>
       <c r="M154">
-        <v>3.84</v>
+        <v>3.51</v>
       </c>
       <c r="N154">
-        <v>94.73999999999999</v>
+        <v>86.62</v>
       </c>
       <c r="O154">
-        <v>14.37</v>
+        <v>13.29</v>
       </c>
     </row>
     <row r="155" spans="1:15">
@@ -10608,16 +10608,16 @@
         <v>42</v>
       </c>
       <c r="D218">
-        <v>184</v>
+        <v>218</v>
       </c>
       <c r="E218">
-        <v>192</v>
+        <v>226</v>
       </c>
       <c r="F218">
-        <v>192</v>
+        <v>226</v>
       </c>
       <c r="G218">
-        <v>1208.08</v>
+        <v>1401.54</v>
       </c>
       <c r="H218">
         <v>37</v>
@@ -10635,13 +10635,13 @@
         <v>1.63</v>
       </c>
       <c r="M218">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="N218">
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
       <c r="O218">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="219" spans="1:15">
@@ -12085,16 +12085,16 @@
         <v>42</v>
       </c>
       <c r="D253">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="E253">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="F253">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="G253">
-        <v>2329.32</v>
+        <v>2425.2</v>
       </c>
       <c r="H253">
         <v>632</v>
@@ -12112,13 +12112,13 @@
         <v>10.14</v>
       </c>
       <c r="M253">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="N253">
-        <v>15.52</v>
+        <v>14.9</v>
       </c>
       <c r="O253">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="254" spans="1:15">
@@ -12543,16 +12543,16 @@
         <v>42</v>
       </c>
       <c r="D263">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E263">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F263">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G263">
-        <v>157.92</v>
+        <v>191.76</v>
       </c>
       <c r="H263">
         <v>24</v>
@@ -12570,13 +12570,13 @@
         <v>7.84</v>
       </c>
       <c r="M263">
-        <v>0.86</v>
+        <v>0.71</v>
       </c>
       <c r="N263">
-        <v>6.72</v>
+        <v>5.54</v>
       </c>
       <c r="O263">
-        <v>1.19</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="264" spans="1:15">
@@ -12995,16 +12995,16 @@
         <v>42</v>
       </c>
       <c r="D273">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E273">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F273">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G273">
-        <v>530.16</v>
+        <v>547.08</v>
       </c>
       <c r="H273">
         <v>75</v>
@@ -13022,13 +13022,13 @@
         <v>2.52</v>
       </c>
       <c r="M273">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="N273">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="O273">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="274" spans="1:15">
@@ -13456,16 +13456,16 @@
         <v>42</v>
       </c>
       <c r="D283">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E283">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F283">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G283">
-        <v>445.56</v>
+        <v>451.2</v>
       </c>
       <c r="H283">
         <v>75</v>
@@ -13483,10 +13483,10 @@
         <v>2.33</v>
       </c>
       <c r="M283">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N283">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="O283">
         <v>0.39</v>
@@ -13908,16 +13908,16 @@
         <v>42</v>
       </c>
       <c r="D293">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E293">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F293">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G293">
-        <v>417.36</v>
+        <v>428.64</v>
       </c>
       <c r="H293">
         <v>211</v>
@@ -13935,13 +13935,13 @@
         <v>8.720000000000001</v>
       </c>
       <c r="M293">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="N293">
-        <v>24.85</v>
+        <v>24.2</v>
       </c>
       <c r="O293">
-        <v>4.41</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="294" spans="1:15">
@@ -15942,16 +15942,16 @@
         <v>42</v>
       </c>
       <c r="D338">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E338">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F338">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="G338">
-        <v>626.04</v>
+        <v>654.24</v>
       </c>
       <c r="H338">
         <v>14</v>
@@ -15969,13 +15969,13 @@
         <v>18.49</v>
       </c>
       <c r="M338">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="N338">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="O338">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="339" spans="1:15">
@@ -16130,16 +16130,16 @@
         <v>42</v>
       </c>
       <c r="D342">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="E342">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="F342">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="G342">
-        <v>2735.85</v>
+        <v>2825.55</v>
       </c>
       <c r="H342">
         <v>220</v>
@@ -16157,10 +16157,10 @@
         <v>2.12</v>
       </c>
       <c r="M342">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="N342">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="O342">
         <v>0.17</v>
@@ -16271,16 +16271,16 @@
         <v>42</v>
       </c>
       <c r="D345">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E345">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F345">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G345">
-        <v>206.31</v>
+        <v>224.25</v>
       </c>
       <c r="H345">
         <v>18</v>
@@ -16298,7 +16298,7 @@
         <v>0</v>
       </c>
       <c r="M345">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="N345">
         <v>0</v>
@@ -16456,16 +16456,16 @@
         <v>42</v>
       </c>
       <c r="D349">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E349">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F349">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G349">
-        <v>825.24</v>
+        <v>861.12</v>
       </c>
       <c r="H349">
         <v>41</v>
@@ -16483,10 +16483,10 @@
         <v>0.82</v>
       </c>
       <c r="M349">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="N349">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="O349">
         <v>0.04</v>
@@ -16832,16 +16832,16 @@
         <v>42</v>
       </c>
       <c r="D357">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E357">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F357">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G357">
-        <v>816.27</v>
+        <v>825.24</v>
       </c>
       <c r="H357">
         <v>78</v>
@@ -16859,10 +16859,10 @@
         <v>1.66</v>
       </c>
       <c r="M357">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="N357">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="O357">
         <v>0.16</v>
@@ -17648,16 +17648,16 @@
         <v>42</v>
       </c>
       <c r="D375">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E375">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F375">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G375">
-        <v>134.55</v>
+        <v>161.46</v>
       </c>
       <c r="H375">
         <v>3</v>
@@ -17675,7 +17675,7 @@
         <v>0</v>
       </c>
       <c r="M375">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="N375">
         <v>0</v>
@@ -17695,13 +17695,13 @@
         <v>42</v>
       </c>
       <c r="D376">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E376">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F376">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G376">
         <v>0</v>
@@ -17722,7 +17722,7 @@
         <v>0</v>
       </c>
       <c r="M376">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="N376">
         <v>0</v>
@@ -17783,13 +17783,13 @@
         <v>42</v>
       </c>
       <c r="D378">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E378">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F378">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G378">
         <v>0</v>
@@ -18091,16 +18091,16 @@
         <v>42</v>
       </c>
       <c r="D385">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E385">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F385">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G385">
-        <v>141.9</v>
+        <v>146.63</v>
       </c>
       <c r="H385">
         <v>75</v>
@@ -18118,13 +18118,13 @@
         <v>11.13</v>
       </c>
       <c r="M385">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="N385">
-        <v>27.82</v>
+        <v>26.93</v>
       </c>
       <c r="O385">
-        <v>5.88</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="386" spans="1:15">
@@ -18578,16 +18578,16 @@
         <v>42</v>
       </c>
       <c r="D396">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E396">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F396">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G396">
-        <v>4.73</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="H396">
         <v>17</v>
@@ -18605,13 +18605,13 @@
         <v>5.17</v>
       </c>
       <c r="M396">
-        <v>17</v>
+        <v>8.5</v>
       </c>
       <c r="N396">
-        <v>87.94</v>
+        <v>43.97</v>
       </c>
       <c r="O396">
-        <v>18.59</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="397" spans="1:15">
@@ -20127,16 +20127,16 @@
         <v>42</v>
       </c>
       <c r="D431">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E431">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F431">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G431">
-        <v>49.63</v>
+        <v>56.72</v>
       </c>
       <c r="H431">
         <v>7</v>
@@ -20154,7 +20154,7 @@
         <v>0</v>
       </c>
       <c r="M431">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="N431">
         <v>0</v>
@@ -20309,16 +20309,16 @@
         <v>42</v>
       </c>
       <c r="D435">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E435">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F435">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G435">
-        <v>14.18</v>
+        <v>21.27</v>
       </c>
       <c r="H435">
         <v>1</v>
@@ -20336,7 +20336,7 @@
         <v>0</v>
       </c>
       <c r="M435">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="N435">
         <v>0</v>
@@ -21329,13 +21329,13 @@
         <v>42</v>
       </c>
       <c r="D459">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E459">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F459">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G459">
         <v>0</v>
@@ -21356,10 +21356,10 @@
         <v>2.43</v>
       </c>
       <c r="M459">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="N459">
-        <v>4</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="460" spans="1:14">
@@ -21906,13 +21906,13 @@
         <v>42</v>
       </c>
       <c r="D473">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E473">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F473">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G473">
         <v>0</v>
@@ -21933,7 +21933,7 @@
         <v>0</v>
       </c>
       <c r="M473">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="N473">
         <v>0</v>
@@ -21997,16 +21997,16 @@
         <v>42</v>
       </c>
       <c r="D475">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="E475">
-        <v>451</v>
+        <v>469</v>
       </c>
       <c r="F475">
-        <v>451</v>
+        <v>469</v>
       </c>
       <c r="G475">
-        <v>2850.01</v>
+        <v>2974.39</v>
       </c>
       <c r="H475">
         <v>302</v>
@@ -22024,10 +22024,10 @@
         <v>1.64</v>
       </c>
       <c r="M475">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="N475">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="O475">
         <v>0.17</v>
@@ -22091,16 +22091,16 @@
         <v>42</v>
       </c>
       <c r="D477">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E477">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F477">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G477">
-        <v>143.66</v>
+        <v>178.21</v>
       </c>
       <c r="H477">
         <v>14</v>
@@ -22118,7 +22118,7 @@
         <v>0</v>
       </c>
       <c r="M477">
-        <v>0.54</v>
+        <v>0.45</v>
       </c>
       <c r="N477">
         <v>0</v>
@@ -22182,16 +22182,16 @@
         <v>42</v>
       </c>
       <c r="D479">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E479">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="F479">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G479">
-        <v>851.27</v>
+        <v>885.8200000000001</v>
       </c>
       <c r="H479">
         <v>56</v>
@@ -22209,10 +22209,10 @@
         <v>0.77</v>
       </c>
       <c r="M479">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="N479">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="O479">
         <v>0.05</v>
@@ -22370,16 +22370,16 @@
         <v>42</v>
       </c>
       <c r="D483">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E483">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F483">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G483">
-        <v>826.88</v>
+        <v>840.7</v>
       </c>
       <c r="H483">
         <v>116</v>
@@ -22397,10 +22397,10 @@
         <v>1.53</v>
       </c>
       <c r="M483">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="N483">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="O483">
         <v>0.21</v>
@@ -22558,16 +22558,16 @@
         <v>42</v>
       </c>
       <c r="D487">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E487">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F487">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G487">
-        <v>65.5</v>
+        <v>72.41</v>
       </c>
       <c r="H487">
         <v>13</v>
@@ -22585,13 +22585,13 @@
         <v>5.71</v>
       </c>
       <c r="M487">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="N487">
-        <v>7.42</v>
+        <v>6.75</v>
       </c>
       <c r="O487">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="488" spans="1:15">
@@ -22743,16 +22743,16 @@
         <v>42</v>
       </c>
       <c r="D491">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E491">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F491">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G491">
-        <v>157.13</v>
+        <v>191.68</v>
       </c>
       <c r="H491">
         <v>0</v>
@@ -22928,16 +22928,16 @@
         <v>42</v>
       </c>
       <c r="D495">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E495">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F495">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G495">
-        <v>131.22</v>
+        <v>140.94</v>
       </c>
       <c r="H495">
         <v>112</v>
@@ -22955,13 +22955,13 @@
         <v>12.64</v>
       </c>
       <c r="M495">
-        <v>4.15</v>
+        <v>3.86</v>
       </c>
       <c r="N495">
-        <v>52.45</v>
+        <v>48.83</v>
       </c>
       <c r="O495">
-        <v>10.79</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="496" spans="1:15">
@@ -23665,16 +23665,16 @@
         <v>42</v>
       </c>
       <c r="D511">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E511">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F511">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G511">
-        <v>34.02</v>
+        <v>38.88</v>
       </c>
       <c r="H511">
         <v>36</v>
@@ -23692,13 +23692,13 @@
         <v>3.3</v>
       </c>
       <c r="M511">
-        <v>5.14</v>
+        <v>4.5</v>
       </c>
       <c r="N511">
-        <v>16.99</v>
+        <v>14.87</v>
       </c>
       <c r="O511">
-        <v>3.5</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="512" spans="1:15">
@@ -24041,16 +24041,16 @@
         <v>42</v>
       </c>
       <c r="D519">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E519">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F519">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G519">
-        <v>9.720000000000001</v>
+        <v>14.58</v>
       </c>
       <c r="H519">
         <v>18</v>
@@ -24068,13 +24068,13 @@
         <v>17.86</v>
       </c>
       <c r="M519">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N519">
-        <v>160.75</v>
+        <v>107.17</v>
       </c>
       <c r="O519">
-        <v>33.08</v>
+        <v>22.05</v>
       </c>
     </row>
     <row r="520" spans="1:15">
@@ -25262,16 +25262,16 @@
         <v>42</v>
       </c>
       <c r="D546">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="E546">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="F546">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="G546">
-        <v>1625.97</v>
+        <v>1691.27</v>
       </c>
       <c r="H546">
         <v>289</v>
@@ -25289,13 +25289,13 @@
         <v>5.83</v>
       </c>
       <c r="M546">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="N546">
-        <v>6.77</v>
+        <v>6.51</v>
       </c>
       <c r="O546">
-        <v>1.04</v>
+        <v>1</v>
       </c>
     </row>
     <row r="547" spans="1:15">
@@ -25732,16 +25732,16 @@
         <v>42</v>
       </c>
       <c r="D556">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E556">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F556">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G556">
-        <v>104.48</v>
+        <v>137.13</v>
       </c>
       <c r="H556">
         <v>7</v>
@@ -25759,13 +25759,13 @@
         <v>5.57</v>
       </c>
       <c r="M556">
-        <v>0.44</v>
+        <v>0.33</v>
       </c>
       <c r="N556">
-        <v>2.44</v>
+        <v>1.86</v>
       </c>
       <c r="O556">
-        <v>0.37</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="557" spans="1:15">
@@ -26202,16 +26202,16 @@
         <v>42</v>
       </c>
       <c r="D566">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E566">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F566">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G566">
-        <v>470.16</v>
+        <v>476.69</v>
       </c>
       <c r="H566">
         <v>43</v>
@@ -26229,13 +26229,13 @@
         <v>2.48</v>
       </c>
       <c r="M566">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="N566">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="O566">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="567" spans="1:15">
@@ -27048,16 +27048,16 @@
         <v>42</v>
       </c>
       <c r="D584">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E584">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F584">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G584">
-        <v>385.27</v>
+        <v>398.33</v>
       </c>
       <c r="H584">
         <v>122</v>
@@ -27075,13 +27075,13 @@
         <v>3.39</v>
       </c>
       <c r="M584">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="N584">
-        <v>7.02</v>
+        <v>6.79</v>
       </c>
       <c r="O584">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="585" spans="1:15">
@@ -29015,16 +29015,16 @@
         <v>42</v>
       </c>
       <c r="D627">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E627">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F627">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G627">
-        <v>150.19</v>
+        <v>163.25</v>
       </c>
       <c r="H627">
         <v>3</v>
@@ -29042,7 +29042,7 @@
         <v>0</v>
       </c>
       <c r="M627">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="N627">
         <v>0</v>
@@ -29767,16 +29767,16 @@
         <v>42</v>
       </c>
       <c r="D643">
-        <v>1845</v>
+        <v>1980</v>
       </c>
       <c r="E643">
-        <v>2508</v>
+        <v>2715</v>
       </c>
       <c r="F643">
-        <v>2805</v>
+        <v>3015</v>
       </c>
       <c r="G643">
-        <v>17882.14</v>
+        <v>19157.55</v>
       </c>
       <c r="H643">
         <v>2991</v>
@@ -29794,13 +29794,13 @@
         <v>7.77</v>
       </c>
       <c r="M643">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="N643">
-        <v>9.27</v>
+        <v>8.56</v>
       </c>
       <c r="O643">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="644" spans="1:15">
@@ -30519,16 +30519,16 @@
         <v>42</v>
       </c>
       <c r="D659">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="E659">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="F659">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="G659">
-        <v>790.95</v>
+        <v>968.58</v>
       </c>
       <c r="H659">
         <v>189</v>
@@ -30546,13 +30546,13 @@
         <v>1.91</v>
       </c>
       <c r="M659">
-        <v>1.91</v>
+        <v>1.49</v>
       </c>
       <c r="N659">
-        <v>3.64</v>
+        <v>2.84</v>
       </c>
       <c r="O659">
-        <v>0.46</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="660" spans="1:15">
@@ -31271,16 +31271,16 @@
         <v>42</v>
       </c>
       <c r="D675">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="E675">
-        <v>435</v>
+        <v>472</v>
       </c>
       <c r="F675">
-        <v>530</v>
+        <v>568</v>
       </c>
       <c r="G675">
-        <v>3483.77</v>
+        <v>3725.5</v>
       </c>
       <c r="H675">
         <v>331</v>
@@ -31298,13 +31298,13 @@
         <v>1.82</v>
       </c>
       <c r="M675">
-        <v>0.76</v>
+        <v>0.7</v>
       </c>
       <c r="N675">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="O675">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="676" spans="1:15">
@@ -32023,16 +32023,16 @@
         <v>42</v>
       </c>
       <c r="D691">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="E691">
-        <v>454</v>
+        <v>483</v>
       </c>
       <c r="F691">
-        <v>517</v>
+        <v>546</v>
       </c>
       <c r="G691">
-        <v>3367.37</v>
+        <v>3538.37</v>
       </c>
       <c r="H691">
         <v>416</v>
@@ -32050,13 +32050,13 @@
         <v>1.59</v>
       </c>
       <c r="M691">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="N691">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="O691">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="692" spans="1:15">
@@ -32775,16 +32775,16 @@
         <v>42</v>
       </c>
       <c r="D707">
-        <v>557</v>
+        <v>581</v>
       </c>
       <c r="E707">
-        <v>771</v>
+        <v>812</v>
       </c>
       <c r="F707">
-        <v>839</v>
+        <v>881</v>
       </c>
       <c r="G707">
-        <v>5395.44</v>
+        <v>5651.74</v>
       </c>
       <c r="H707">
         <v>1097</v>
@@ -32802,13 +32802,13 @@
         <v>4.91</v>
       </c>
       <c r="M707">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="N707">
-        <v>6.99</v>
+        <v>6.64</v>
       </c>
       <c r="O707">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="708" spans="1:15">
@@ -33527,16 +33527,16 @@
         <v>42</v>
       </c>
       <c r="D723">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E723">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="F723">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="G723">
-        <v>1328.11</v>
+        <v>1382.47</v>
       </c>
       <c r="H723">
         <v>354</v>
@@ -33554,13 +33554,13 @@
         <v>15.01</v>
       </c>
       <c r="M723">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="N723">
-        <v>25.07</v>
+        <v>24.05</v>
       </c>
       <c r="O723">
-        <v>4</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="724" spans="1:15">
@@ -34279,16 +34279,16 @@
         <v>42</v>
       </c>
       <c r="D739">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E739">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F739">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G739">
-        <v>858.96</v>
+        <v>888.85</v>
       </c>
       <c r="H739">
         <v>400</v>
@@ -34306,13 +34306,13 @@
         <v>16.43</v>
       </c>
       <c r="M739">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="N739">
-        <v>50.95</v>
+        <v>49.05</v>
       </c>
       <c r="O739">
-        <v>7.65</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="740" spans="1:15">
@@ -35774,16 +35774,16 @@
         <v>42</v>
       </c>
       <c r="D771">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E771">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F771">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G771">
-        <v>113.73</v>
+        <v>119.77</v>
       </c>
       <c r="H771">
         <v>38</v>
@@ -35801,13 +35801,13 @@
         <v>37.52</v>
       </c>
       <c r="M771">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="N771">
-        <v>71.29000000000001</v>
+        <v>67.89</v>
       </c>
       <c r="O771">
-        <v>12.54</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="772" spans="1:15">
@@ -36508,16 +36508,16 @@
         <v>42</v>
       </c>
       <c r="D787">
-        <v>313</v>
+        <v>359</v>
       </c>
       <c r="E787">
-        <v>360</v>
+        <v>417</v>
       </c>
       <c r="F787">
-        <v>387</v>
+        <v>444</v>
       </c>
       <c r="G787">
-        <v>2372.52</v>
+        <v>2710.98</v>
       </c>
       <c r="H787">
         <v>61</v>
@@ -36535,13 +36535,13 @@
         <v>5.23</v>
       </c>
       <c r="M787">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="N787">
-        <v>0.89</v>
+        <v>0.77</v>
       </c>
       <c r="O787">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
     </row>
   </sheetData>

--- a/slab_month_product.xlsx
+++ b/slab_month_product.xlsx
@@ -1913,7 +1913,7 @@
         <v>28.77</v>
       </c>
       <c r="R18">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="S18">
         <v>29940.51</v>
@@ -1925,7 +1925,7 @@
         <v>55.6</v>
       </c>
       <c r="V18">
-        <v>24.52</v>
+        <v>24.54</v>
       </c>
       <c r="W18">
         <v>35.73</v>
@@ -2221,7 +2221,7 @@
         <v>29.15</v>
       </c>
       <c r="R22">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="S22">
         <v>97259.25999999999</v>
@@ -2233,7 +2233,7 @@
         <v>91.09999999999999</v>
       </c>
       <c r="V22">
-        <v>29.96</v>
+        <v>29.97</v>
       </c>
       <c r="W22">
         <v>86.68000000000001</v>
@@ -2298,7 +2298,7 @@
         <v>15.14</v>
       </c>
       <c r="R23">
-        <v>6886</v>
+        <v>6884</v>
       </c>
       <c r="S23">
         <v>106101.54</v>
@@ -2375,7 +2375,7 @@
         <v>8.109999999999999</v>
       </c>
       <c r="R24">
-        <v>2833</v>
+        <v>2832</v>
       </c>
       <c r="S24">
         <v>42315.21</v>
@@ -2422,34 +2422,34 @@
         <v>17453.35</v>
       </c>
       <c r="H25">
-        <v>1866</v>
+        <v>1863</v>
       </c>
       <c r="I25">
-        <v>64996.83</v>
+        <v>64840.91</v>
       </c>
       <c r="J25">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="K25">
-        <v>57.3</v>
+        <v>57.2</v>
       </c>
       <c r="L25">
-        <v>34.83</v>
+        <v>34.8</v>
       </c>
       <c r="M25">
-        <v>2837</v>
+        <v>2836</v>
       </c>
       <c r="N25">
-        <v>99665.47</v>
+        <v>99549.52</v>
       </c>
       <c r="O25">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="P25">
-        <v>67.59999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="Q25">
-        <v>35.13</v>
+        <v>35.1</v>
       </c>
       <c r="R25">
         <v>4196</v>
@@ -2458,10 +2458,10 @@
         <v>138844.97</v>
       </c>
       <c r="T25">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="U25">
-        <v>71.3</v>
+        <v>71.2</v>
       </c>
       <c r="V25">
         <v>33.09</v>
@@ -2499,10 +2499,10 @@
         <v>6274.38</v>
       </c>
       <c r="H26">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="I26">
-        <v>26707.54</v>
+        <v>26623.5</v>
       </c>
       <c r="J26">
         <v>403</v>
@@ -2511,13 +2511,13 @@
         <v>50.7</v>
       </c>
       <c r="L26">
-        <v>24.8</v>
+        <v>24.77</v>
       </c>
       <c r="M26">
-        <v>1843</v>
+        <v>1841</v>
       </c>
       <c r="N26">
-        <v>32837</v>
+        <v>32800.92</v>
       </c>
       <c r="O26">
         <v>609</v>
@@ -2529,7 +2529,7 @@
         <v>17.82</v>
       </c>
       <c r="R26">
-        <v>1950</v>
+        <v>1948</v>
       </c>
       <c r="S26">
         <v>33785.59</v>
@@ -2541,13 +2541,13 @@
         <v>77.2</v>
       </c>
       <c r="V26">
-        <v>17.33</v>
+        <v>17.34</v>
       </c>
       <c r="W26">
         <v>32.52</v>
       </c>
       <c r="X26">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Y26">
         <v>5.38</v>
@@ -7152,10 +7152,10 @@
         <v>1020</v>
       </c>
       <c r="H89">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I89">
-        <v>23748.68</v>
+        <v>23708.71</v>
       </c>
       <c r="J89">
         <v>48</v>
@@ -7164,7 +7164,7 @@
         <v>64.90000000000001</v>
       </c>
       <c r="L89">
-        <v>107.46</v>
+        <v>107.77</v>
       </c>
       <c r="M89">
         <v>377</v>
@@ -7229,10 +7229,10 @@
         <v>590.53</v>
       </c>
       <c r="H90">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I90">
-        <v>6531.06</v>
+        <v>6447.02</v>
       </c>
       <c r="J90">
         <v>42</v>
@@ -7241,7 +7241,7 @@
         <v>50.6</v>
       </c>
       <c r="L90">
-        <v>33.84</v>
+        <v>33.58</v>
       </c>
       <c r="M90">
         <v>308</v>
@@ -7875,7 +7875,7 @@
         <v>22.43</v>
       </c>
       <c r="R98">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="S98">
         <v>3688.57</v>
@@ -7887,13 +7887,13 @@
         <v>96.40000000000001</v>
       </c>
       <c r="V98">
-        <v>14.52</v>
+        <v>14.58</v>
       </c>
       <c r="W98">
         <v>127.19</v>
       </c>
       <c r="X98">
-        <v>8.76</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="Y98">
         <v>20.96</v>
@@ -8260,7 +8260,7 @@
         <v>7.02</v>
       </c>
       <c r="R103">
-        <v>1718</v>
+        <v>1716</v>
       </c>
       <c r="S103">
         <v>13575.74</v>
@@ -8272,13 +8272,13 @@
         <v>94.40000000000001</v>
       </c>
       <c r="V103">
-        <v>7.9</v>
+        <v>7.91</v>
       </c>
       <c r="W103">
         <v>22.66</v>
       </c>
       <c r="X103">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="Y103">
         <v>3.67</v>
@@ -8414,7 +8414,7 @@
         <v>19.25</v>
       </c>
       <c r="R105">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="S105">
         <v>26571.8</v>
@@ -8426,7 +8426,7 @@
         <v>73.40000000000001</v>
       </c>
       <c r="V105">
-        <v>17</v>
+        <v>17.01</v>
       </c>
       <c r="W105">
         <v>31.82</v>
@@ -8461,7 +8461,7 @@
         <v>2589.17</v>
       </c>
       <c r="H106">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I106">
         <v>4385.08</v>
@@ -8473,10 +8473,10 @@
         <v>49.8</v>
       </c>
       <c r="L106">
-        <v>10.34</v>
+        <v>10.37</v>
       </c>
       <c r="M106">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="N106">
         <v>5945.62</v>
@@ -8488,10 +8488,10 @@
         <v>79.5</v>
       </c>
       <c r="Q106">
-        <v>7.56</v>
+        <v>7.57</v>
       </c>
       <c r="R106">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="S106">
         <v>6267.61</v>
@@ -8503,7 +8503,7 @@
         <v>80.09999999999999</v>
       </c>
       <c r="V106">
-        <v>7.74</v>
+        <v>7.75</v>
       </c>
       <c r="W106">
         <v>14.41</v>
@@ -10570,7 +10570,7 @@
         <v>93.18000000000001</v>
       </c>
       <c r="R133">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="S133">
         <v>18852.96</v>
@@ -10582,13 +10582,13 @@
         <v>100</v>
       </c>
       <c r="V133">
-        <v>67.33</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="W133">
         <v>1178.31</v>
       </c>
       <c r="X133">
-        <v>17.5</v>
+        <v>17.44</v>
       </c>
       <c r="Y133">
         <v>207.2</v>
@@ -10724,7 +10724,7 @@
         <v>80.93000000000001</v>
       </c>
       <c r="R135">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="S135">
         <v>14582.16</v>
@@ -10736,13 +10736,13 @@
         <v>77.8</v>
       </c>
       <c r="V135">
-        <v>103.42</v>
+        <v>104.16</v>
       </c>
       <c r="W135">
         <v>607.59</v>
       </c>
       <c r="X135">
-        <v>5.88</v>
+        <v>5.83</v>
       </c>
       <c r="Y135">
         <v>75.48</v>
@@ -10863,10 +10863,10 @@
         <v>34.49</v>
       </c>
       <c r="M137">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N137">
-        <v>1800.44</v>
+        <v>1764.36</v>
       </c>
       <c r="O137">
         <v>20</v>
@@ -10875,7 +10875,7 @@
         <v>83.3</v>
       </c>
       <c r="Q137">
-        <v>28.13</v>
+        <v>28.01</v>
       </c>
       <c r="R137">
         <v>70</v>
@@ -12003,49 +12003,49 @@
         <v>2795.22</v>
       </c>
       <c r="H152">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I152">
         <v>1891</v>
       </c>
       <c r="J152">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K152">
-        <v>60.4</v>
+        <v>59.9</v>
       </c>
       <c r="L152">
-        <v>7.39</v>
+        <v>7.42</v>
       </c>
       <c r="M152">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="N152">
         <v>2230.59</v>
       </c>
       <c r="O152">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P152">
-        <v>68.3</v>
+        <v>67.8</v>
       </c>
       <c r="Q152">
-        <v>6.23</v>
+        <v>6.25</v>
       </c>
       <c r="R152">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="S152">
         <v>2898.02</v>
       </c>
       <c r="T152">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="U152">
-        <v>70.3</v>
+        <v>69.8</v>
       </c>
       <c r="V152">
-        <v>6.33</v>
+        <v>6.34</v>
       </c>
       <c r="W152">
         <v>8.94</v>
@@ -12110,7 +12110,7 @@
         <v>3.18</v>
       </c>
       <c r="R153">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="S153">
         <v>578.77</v>
@@ -12122,7 +12122,7 @@
         <v>73.90000000000001</v>
       </c>
       <c r="V153">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="W153">
         <v>3.86</v>
@@ -14464,10 +14464,10 @@
         <v>1276.65</v>
       </c>
       <c r="H184">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I184">
-        <v>18234.84</v>
+        <v>18118.89</v>
       </c>
       <c r="J184">
         <v>62</v>
@@ -14476,13 +14476,13 @@
         <v>57.4</v>
       </c>
       <c r="L184">
-        <v>69.59999999999999</v>
+        <v>69.42</v>
       </c>
       <c r="M184">
         <v>386</v>
       </c>
       <c r="N184">
-        <v>21064.18</v>
+        <v>20948.23</v>
       </c>
       <c r="O184">
         <v>77</v>
@@ -14491,10 +14491,10 @@
         <v>71.3</v>
       </c>
       <c r="Q184">
-        <v>54.57</v>
+        <v>54.27</v>
       </c>
       <c r="R184">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="S184">
         <v>36852.65</v>
@@ -14506,13 +14506,13 @@
         <v>74.09999999999999</v>
       </c>
       <c r="V184">
-        <v>54.52</v>
+        <v>54.35</v>
       </c>
       <c r="W184">
         <v>222</v>
       </c>
       <c r="X184">
-        <v>4.07</v>
+        <v>4.08</v>
       </c>
       <c r="Y184">
         <v>28.87</v>
@@ -18263,7 +18263,7 @@
         <v>13.04</v>
       </c>
       <c r="R234">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="S234">
         <v>32246.22</v>
@@ -18275,7 +18275,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="V234">
-        <v>16.21</v>
+        <v>16.22</v>
       </c>
       <c r="W234">
         <v>47.14</v>
@@ -18340,7 +18340,7 @@
         <v>7.09</v>
       </c>
       <c r="R235">
-        <v>5429</v>
+        <v>5428</v>
       </c>
       <c r="S235">
         <v>37630.23</v>
@@ -18417,7 +18417,7 @@
         <v>4.59</v>
       </c>
       <c r="R236">
-        <v>2327</v>
+        <v>2326</v>
       </c>
       <c r="S236">
         <v>23668.07</v>
@@ -18429,7 +18429,7 @@
         <v>48.4</v>
       </c>
       <c r="V236">
-        <v>10.17</v>
+        <v>10.18</v>
       </c>
       <c r="W236">
         <v>10.79</v>
@@ -18464,49 +18464,49 @@
         <v>7754.45</v>
       </c>
       <c r="H237">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="I237">
-        <v>32899.95</v>
+        <v>32784</v>
       </c>
       <c r="J237">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K237">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="L237">
-        <v>39.21</v>
+        <v>39.22</v>
       </c>
       <c r="M237">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="N237">
-        <v>41844.01</v>
+        <v>41728.06</v>
       </c>
       <c r="O237">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="P237">
-        <v>59.3</v>
+        <v>59.2</v>
       </c>
       <c r="Q237">
-        <v>32.9</v>
+        <v>32.88</v>
       </c>
       <c r="R237">
-        <v>1966</v>
+        <v>1964</v>
       </c>
       <c r="S237">
         <v>69664.8</v>
       </c>
       <c r="T237">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="U237">
-        <v>64.3</v>
+        <v>64.2</v>
       </c>
       <c r="V237">
-        <v>35.43</v>
+        <v>35.47</v>
       </c>
       <c r="W237">
         <v>70.94</v>
@@ -18571,7 +18571,7 @@
         <v>7.47</v>
       </c>
       <c r="R238">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="S238">
         <v>5077.68</v>
@@ -18583,7 +18583,7 @@
         <v>77.09999999999999</v>
       </c>
       <c r="V238">
-        <v>7.39</v>
+        <v>7.4</v>
       </c>
       <c r="W238">
         <v>13.91</v>
@@ -21947,7 +21947,7 @@
         <v>940.73</v>
       </c>
       <c r="H285">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I285">
         <v>359.17</v>
@@ -21959,10 +21959,10 @@
         <v>36.7</v>
       </c>
       <c r="L285">
-        <v>6.09</v>
+        <v>6.19</v>
       </c>
       <c r="M285">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N285">
         <v>413.79</v>
@@ -21974,10 +21974,10 @@
         <v>53.2</v>
       </c>
       <c r="Q285">
-        <v>4.36</v>
+        <v>4.4</v>
       </c>
       <c r="R285">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="S285">
         <v>446.18</v>
@@ -21989,7 +21989,7 @@
         <v>57.8</v>
       </c>
       <c r="V285">
-        <v>4.21</v>
+        <v>4.25</v>
       </c>
       <c r="W285">
         <v>4.02</v>
@@ -24287,7 +24287,7 @@
         <v>6.52</v>
       </c>
       <c r="R315">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="S315">
         <v>8098.69</v>
@@ -24299,7 +24299,7 @@
         <v>93.8</v>
       </c>
       <c r="V315">
-        <v>6.45</v>
+        <v>6.46</v>
       </c>
       <c r="W315">
         <v>18.32</v>
@@ -24441,7 +24441,7 @@
         <v>23.01</v>
       </c>
       <c r="R317">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="S317">
         <v>13865.15</v>
@@ -24453,7 +24453,7 @@
         <v>64.59999999999999</v>
       </c>
       <c r="V317">
-        <v>20.18</v>
+        <v>20.21</v>
       </c>
       <c r="W317">
         <v>34.66</v>
@@ -26588,7 +26588,7 @@
         <v>20.63</v>
       </c>
       <c r="R345">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S345">
         <v>1267.23</v>
@@ -26600,13 +26600,13 @@
         <v>100</v>
       </c>
       <c r="V345">
-        <v>24.85</v>
+        <v>25.34</v>
       </c>
       <c r="W345">
         <v>97.48</v>
       </c>
       <c r="X345">
-        <v>3.92</v>
+        <v>3.85</v>
       </c>
       <c r="Y345">
         <v>17.13</v>
@@ -26742,7 +26742,7 @@
         <v>16.5</v>
       </c>
       <c r="R347">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="S347">
         <v>9310.32</v>
@@ -26754,13 +26754,13 @@
         <v>76.90000000000001</v>
       </c>
       <c r="V347">
-        <v>100.11</v>
+        <v>101.2</v>
       </c>
       <c r="W347">
         <v>716.1799999999999</v>
       </c>
       <c r="X347">
-        <v>7.15</v>
+        <v>7.08</v>
       </c>
       <c r="Y347">
         <v>108.85</v>
@@ -28021,55 +28021,55 @@
         <v>1226.13</v>
       </c>
       <c r="H364">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I364">
         <v>1061.37</v>
       </c>
       <c r="J364">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K364">
-        <v>57</v>
+        <v>56.3</v>
       </c>
       <c r="L364">
-        <v>8.84</v>
+        <v>8.92</v>
       </c>
       <c r="M364">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N364">
         <v>1175.25</v>
       </c>
       <c r="O364">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P364">
-        <v>68.3</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="Q364">
-        <v>7.39</v>
+        <v>7.44</v>
       </c>
       <c r="R364">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="S364">
         <v>1803.58</v>
       </c>
       <c r="T364">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="U364">
-        <v>70.40000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="V364">
-        <v>8.09</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="W364">
         <v>11.94</v>
       </c>
       <c r="X364">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Y364">
         <v>1.47</v>
@@ -28128,7 +28128,7 @@
         <v>2.98</v>
       </c>
       <c r="R365">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="S365">
         <v>160.69</v>
@@ -28140,13 +28140,13 @@
         <v>72.2</v>
       </c>
       <c r="V365">
-        <v>2.77</v>
+        <v>2.82</v>
       </c>
       <c r="W365">
         <v>3.92</v>
       </c>
       <c r="X365">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="Y365">
         <v>0.68</v>
@@ -30482,10 +30482,10 @@
         <v>599.7</v>
       </c>
       <c r="H396">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I396">
-        <v>9894.870000000001</v>
+        <v>9778.92</v>
       </c>
       <c r="J396">
         <v>35</v>
@@ -30494,13 +30494,13 @@
         <v>48.6</v>
       </c>
       <c r="L396">
-        <v>80.45</v>
+        <v>80.16</v>
       </c>
       <c r="M396">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N396">
-        <v>11134.46</v>
+        <v>11018.51</v>
       </c>
       <c r="O396">
         <v>42</v>
@@ -30509,10 +30509,10 @@
         <v>58.3</v>
       </c>
       <c r="Q396">
-        <v>62.91</v>
+        <v>62.61</v>
       </c>
       <c r="R396">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="S396">
         <v>23999.38</v>
@@ -30524,13 +30524,13 @@
         <v>63.9</v>
       </c>
       <c r="V396">
-        <v>70.79000000000001</v>
+        <v>70.59</v>
       </c>
       <c r="W396">
         <v>299.99</v>
       </c>
       <c r="X396">
-        <v>4.24</v>
+        <v>4.25</v>
       </c>
       <c r="Y396">
         <v>40.02</v>
@@ -31290,7 +31290,7 @@
         <v>16.99</v>
       </c>
       <c r="R407">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="S407">
         <v>5133.76</v>
@@ -31302,13 +31302,13 @@
         <v>57</v>
       </c>
       <c r="V407">
-        <v>20.54</v>
+        <v>20.62</v>
       </c>
       <c r="W407">
         <v>44.26</v>
       </c>
       <c r="X407">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="Y407">
         <v>7.8</v>
@@ -31675,7 +31675,7 @@
         <v>57.53</v>
       </c>
       <c r="R412">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="S412">
         <v>63974.41</v>
@@ -31687,7 +31687,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="V412">
-        <v>53.49</v>
+        <v>53.54</v>
       </c>
       <c r="W412">
         <v>153.42</v>
@@ -31722,10 +31722,10 @@
         <v>3530.64</v>
       </c>
       <c r="H413">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="I413">
-        <v>25290.43</v>
+        <v>25250.46</v>
       </c>
       <c r="J413">
         <v>286</v>
@@ -31734,10 +31734,10 @@
         <v>45.9</v>
       </c>
       <c r="L413">
-        <v>49.4</v>
+        <v>49.41</v>
       </c>
       <c r="M413">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="N413">
         <v>35867.09</v>
@@ -31749,7 +31749,7 @@
         <v>57.1</v>
       </c>
       <c r="Q413">
-        <v>45.17</v>
+        <v>45.12</v>
       </c>
       <c r="R413">
         <v>1226</v>
@@ -31799,10 +31799,10 @@
         <v>1923.24</v>
       </c>
       <c r="H414">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I414">
-        <v>18001.66</v>
+        <v>17917.62</v>
       </c>
       <c r="J414">
         <v>175</v>
@@ -31811,10 +31811,10 @@
         <v>52.7</v>
       </c>
       <c r="L414">
-        <v>44.78</v>
+        <v>44.79</v>
       </c>
       <c r="M414">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="N414">
         <v>20219.27</v>
@@ -31826,10 +31826,10 @@
         <v>73.8</v>
       </c>
       <c r="Q414">
-        <v>33.87</v>
+        <v>33.92</v>
       </c>
       <c r="R414">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="S414">
         <v>20849</v>
@@ -31841,13 +31841,13 @@
         <v>74.7</v>
       </c>
       <c r="V414">
-        <v>31.88</v>
+        <v>31.93</v>
       </c>
       <c r="W414">
         <v>61.14</v>
       </c>
       <c r="X414">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Y414">
         <v>10.84</v>
@@ -33720,10 +33720,10 @@
         <v>203.04</v>
       </c>
       <c r="H440">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I440">
-        <v>12791.63</v>
+        <v>12751.66</v>
       </c>
       <c r="J440">
         <v>21</v>
@@ -33732,7 +33732,7 @@
         <v>58.3</v>
       </c>
       <c r="L440">
-        <v>161.92</v>
+        <v>163.48</v>
       </c>
       <c r="M440">
         <v>114</v>
@@ -33797,10 +33797,10 @@
         <v>141</v>
       </c>
       <c r="H441">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I441">
-        <v>4464.96</v>
+        <v>4380.92</v>
       </c>
       <c r="J441">
         <v>14</v>
@@ -33809,7 +33809,7 @@
         <v>56</v>
       </c>
       <c r="L441">
-        <v>44.21</v>
+        <v>43.81</v>
       </c>
       <c r="M441">
         <v>128</v>
@@ -33981,7 +33981,7 @@
         <v>14.46</v>
       </c>
       <c r="R443">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="S443">
         <v>1728.01</v>
@@ -33993,13 +33993,13 @@
         <v>100</v>
       </c>
       <c r="V443">
-        <v>10.54</v>
+        <v>10.6</v>
       </c>
       <c r="W443">
         <v>216</v>
       </c>
       <c r="X443">
-        <v>20.5</v>
+        <v>20.38</v>
       </c>
       <c r="Y443">
         <v>38.3</v>
@@ -34289,7 +34289,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="R447">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="S447">
         <v>3778.55</v>
@@ -34301,13 +34301,13 @@
         <v>93.8</v>
       </c>
       <c r="V447">
-        <v>10.67</v>
+        <v>10.7</v>
       </c>
       <c r="W447">
         <v>28.84</v>
       </c>
       <c r="X447">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="Y447">
         <v>5.11</v>
@@ -34366,7 +34366,7 @@
         <v>26.98</v>
       </c>
       <c r="R448">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="S448">
         <v>9590.709999999999</v>
@@ -34378,13 +34378,13 @@
         <v>63.7</v>
       </c>
       <c r="V448">
-        <v>23.22</v>
+        <v>23.28</v>
       </c>
       <c r="W448">
         <v>42.44</v>
       </c>
       <c r="X448">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Y448">
         <v>7.52</v>
@@ -34413,7 +34413,7 @@
         <v>676.8</v>
       </c>
       <c r="H449">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I449">
         <v>2140.01</v>
@@ -34425,10 +34425,10 @@
         <v>52.1</v>
       </c>
       <c r="L449">
-        <v>17.4</v>
+        <v>17.54</v>
       </c>
       <c r="M449">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N449">
         <v>2877.91</v>
@@ -34440,10 +34440,10 @@
         <v>76.5</v>
       </c>
       <c r="Q449">
-        <v>13.64</v>
+        <v>13.7</v>
       </c>
       <c r="R449">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="S449">
         <v>3133.95</v>
@@ -34455,13 +34455,13 @@
         <v>78.2</v>
       </c>
       <c r="V449">
-        <v>14.25</v>
+        <v>14.31</v>
       </c>
       <c r="W449">
         <v>26.12</v>
       </c>
       <c r="X449">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Y449">
         <v>4.63</v>
@@ -37413,7 +37413,7 @@
         <v>61.03</v>
       </c>
       <c r="M488">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N488">
         <v>6285.15</v>
@@ -37425,10 +37425,10 @@
         <v>64.59999999999999</v>
       </c>
       <c r="Q488">
-        <v>48.72</v>
+        <v>48.35</v>
       </c>
       <c r="R488">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="S488">
         <v>8862.18</v>
@@ -37440,13 +37440,13 @@
         <v>68.8</v>
       </c>
       <c r="V488">
-        <v>39.21</v>
+        <v>39.04</v>
       </c>
       <c r="W488">
         <v>184.63</v>
       </c>
       <c r="X488">
-        <v>4.71</v>
+        <v>4.73</v>
       </c>
       <c r="Y488">
         <v>32.74</v>
@@ -37706,7 +37706,7 @@
         <v>4637.49</v>
       </c>
       <c r="H492">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I492">
         <v>3203.56</v>
@@ -37718,10 +37718,10 @@
         <v>44.6</v>
       </c>
       <c r="L492">
-        <v>9.92</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="M492">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N492">
         <v>17344.18</v>
@@ -37733,10 +37733,10 @@
         <v>55.2</v>
       </c>
       <c r="Q492">
-        <v>35.11</v>
+        <v>35.04</v>
       </c>
       <c r="R492">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="S492">
         <v>19052.38</v>
@@ -37748,13 +37748,13 @@
         <v>57.4</v>
       </c>
       <c r="V492">
-        <v>30.63</v>
+        <v>30.58</v>
       </c>
       <c r="W492">
         <v>36.85</v>
       </c>
       <c r="X492">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Y492">
         <v>4.11</v>
@@ -38156,7 +38156,7 @@
         <v>852.15</v>
       </c>
       <c r="H498">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I498">
         <v>159.86</v>
@@ -38168,10 +38168,10 @@
         <v>35.8</v>
       </c>
       <c r="L498">
-        <v>3.81</v>
+        <v>3.72</v>
       </c>
       <c r="M498">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N498">
         <v>216.86</v>
@@ -38183,10 +38183,10 @@
         <v>47.4</v>
       </c>
       <c r="Q498">
-        <v>3.61</v>
+        <v>3.56</v>
       </c>
       <c r="R498">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="S498">
         <v>235.82</v>
@@ -38198,13 +38198,13 @@
         <v>49.5</v>
       </c>
       <c r="V498">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
       <c r="W498">
         <v>2.48</v>
       </c>
       <c r="X498">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="Y498">
         <v>0.28</v>
@@ -44730,19 +44730,19 @@
         <v>0</v>
       </c>
       <c r="M587">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N587">
-        <v>36.08</v>
+        <v>0</v>
       </c>
       <c r="O587">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P587">
-        <v>37.5</v>
+        <v>33.3</v>
       </c>
       <c r="Q587">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="R587">
         <v>17</v>
@@ -45369,19 +45369,19 @@
         <v>0</v>
       </c>
       <c r="M596">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N596">
-        <v>36.08</v>
+        <v>0</v>
       </c>
       <c r="O596">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P596">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
       <c r="Q596">
-        <v>18.04</v>
+        <v>0</v>
       </c>
       <c r="R596">
         <v>4</v>
@@ -50908,7 +50908,7 @@
         <v>6</v>
       </c>
       <c r="R670">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S670">
         <v>187.07</v>
@@ -50920,13 +50920,13 @@
         <v>44.4</v>
       </c>
       <c r="V670">
-        <v>5.34</v>
+        <v>5.2</v>
       </c>
       <c r="W670">
         <v>5.2</v>
       </c>
       <c r="X670">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="Y670">
         <v>0.8</v>
@@ -53448,7 +53448,7 @@
         <v>2.12</v>
       </c>
       <c r="R704">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S704">
         <v>54.06</v>
@@ -53460,13 +53460,13 @@
         <v>41.2</v>
       </c>
       <c r="V704">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="W704">
         <v>3.18</v>
       </c>
       <c r="X704">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y704">
         <v>0.49</v>

--- a/slab_month_product.xlsx
+++ b/slab_month_product.xlsx
@@ -3727,16 +3727,16 @@
         <v>53</v>
       </c>
       <c r="D43">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E43">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F43">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="G43">
-        <v>270.2</v>
+        <v>202.9</v>
       </c>
       <c r="H43">
         <v>17</v>
@@ -3748,7 +3748,7 @@
         <v>8</v>
       </c>
       <c r="K43">
-        <v>29.6</v>
+        <v>42.1</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -3763,7 +3763,7 @@
         <v>8</v>
       </c>
       <c r="P43">
-        <v>29.6</v>
+        <v>42.1</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -3778,7 +3778,7 @@
         <v>8</v>
       </c>
       <c r="U43">
-        <v>29.6</v>
+        <v>42.1</v>
       </c>
       <c r="V43">
         <v>0</v>
@@ -3787,7 +3787,7 @@
         <v>0</v>
       </c>
       <c r="X43">
-        <v>0.46</v>
+        <v>0.65</v>
       </c>
       <c r="Y43">
         <v>0</v>
@@ -6050,16 +6050,16 @@
         <v>53</v>
       </c>
       <c r="D75">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E75">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="F75">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="G75">
-        <v>2157.98</v>
+        <v>2197.41</v>
       </c>
       <c r="H75">
         <v>81</v>
@@ -6071,7 +6071,7 @@
         <v>49</v>
       </c>
       <c r="K75">
-        <v>20.6</v>
+        <v>20.3</v>
       </c>
       <c r="L75">
         <v>1.37</v>
@@ -6086,7 +6086,7 @@
         <v>49</v>
       </c>
       <c r="P75">
-        <v>20.6</v>
+        <v>20.3</v>
       </c>
       <c r="Q75">
         <v>1.37</v>
@@ -6101,7 +6101,7 @@
         <v>49</v>
       </c>
       <c r="U75">
-        <v>20.6</v>
+        <v>20.3</v>
       </c>
       <c r="V75">
         <v>1.37</v>
@@ -6110,7 +6110,7 @@
         <v>0.35</v>
       </c>
       <c r="X75">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="Y75">
         <v>0.05</v>
@@ -8514,16 +8514,16 @@
         <v>53</v>
       </c>
       <c r="D107">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="E107">
-        <v>1150</v>
+        <v>1153</v>
       </c>
       <c r="F107">
-        <v>1232</v>
+        <v>1235</v>
       </c>
       <c r="G107">
-        <v>7893.89</v>
+        <v>7910.38</v>
       </c>
       <c r="H107">
         <v>715</v>
@@ -8535,7 +8535,7 @@
         <v>337</v>
       </c>
       <c r="K107">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="L107">
         <v>2.03</v>
@@ -8550,7 +8550,7 @@
         <v>337</v>
       </c>
       <c r="P107">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="Q107">
         <v>2.03</v>
@@ -8565,7 +8565,7 @@
         <v>337</v>
       </c>
       <c r="U107">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="V107">
         <v>2.03</v>
@@ -12133,16 +12133,16 @@
         <v>53</v>
       </c>
       <c r="D154">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E154">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="F154">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="G154">
-        <v>4611.56</v>
+        <v>4622.94</v>
       </c>
       <c r="H154">
         <v>421</v>
@@ -12154,7 +12154,7 @@
         <v>199</v>
       </c>
       <c r="K154">
-        <v>46.5</v>
+        <v>46.3</v>
       </c>
       <c r="L154">
         <v>2.04</v>
@@ -12169,7 +12169,7 @@
         <v>199</v>
       </c>
       <c r="P154">
-        <v>46.5</v>
+        <v>46.3</v>
       </c>
       <c r="Q154">
         <v>2.04</v>
@@ -12184,13 +12184,13 @@
         <v>199</v>
       </c>
       <c r="U154">
-        <v>46.5</v>
+        <v>46.3</v>
       </c>
       <c r="V154">
         <v>2.04</v>
       </c>
       <c r="W154">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X154">
         <v>0.66</v>
@@ -19677,16 +19677,16 @@
         <v>53</v>
       </c>
       <c r="D254">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E254">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F254">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G254">
-        <v>145.5</v>
+        <v>111.36</v>
       </c>
       <c r="H254">
         <v>11</v>
@@ -19698,7 +19698,7 @@
         <v>5</v>
       </c>
       <c r="K254">
-        <v>23.8</v>
+        <v>33.3</v>
       </c>
       <c r="L254">
         <v>0</v>
@@ -19713,7 +19713,7 @@
         <v>5</v>
       </c>
       <c r="P254">
-        <v>23.8</v>
+        <v>33.3</v>
       </c>
       <c r="Q254">
         <v>0</v>
@@ -19728,7 +19728,7 @@
         <v>5</v>
       </c>
       <c r="U254">
-        <v>23.8</v>
+        <v>33.3</v>
       </c>
       <c r="V254">
         <v>0</v>
@@ -19737,7 +19737,7 @@
         <v>0</v>
       </c>
       <c r="X254">
-        <v>0.52</v>
+        <v>0.73</v>
       </c>
       <c r="Y254">
         <v>0</v>
@@ -21994,16 +21994,16 @@
         <v>53</v>
       </c>
       <c r="D286">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E286">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F286">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G286">
-        <v>745.66</v>
+        <v>757.04</v>
       </c>
       <c r="H286">
         <v>24</v>
@@ -22015,7 +22015,7 @@
         <v>20</v>
       </c>
       <c r="K286">
-        <v>16.1</v>
+        <v>15.9</v>
       </c>
       <c r="L286">
         <v>1.62</v>
@@ -22030,7 +22030,7 @@
         <v>20</v>
       </c>
       <c r="P286">
-        <v>16.1</v>
+        <v>15.9</v>
       </c>
       <c r="Q286">
         <v>1.62</v>
@@ -22045,7 +22045,7 @@
         <v>20</v>
       </c>
       <c r="U286">
-        <v>16.1</v>
+        <v>15.9</v>
       </c>
       <c r="V286">
         <v>1.62</v>
@@ -22054,7 +22054,7 @@
         <v>0.3</v>
       </c>
       <c r="X286">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="Y286">
         <v>0.05</v>
@@ -24458,16 +24458,16 @@
         <v>53</v>
       </c>
       <c r="D318">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E318">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F318">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="G318">
-        <v>1983.9</v>
+        <v>1995.28</v>
       </c>
       <c r="H318">
         <v>271</v>
@@ -24479,7 +24479,7 @@
         <v>135</v>
       </c>
       <c r="K318">
-        <v>50.2</v>
+        <v>49.8</v>
       </c>
       <c r="L318">
         <v>1.49</v>
@@ -24494,7 +24494,7 @@
         <v>135</v>
       </c>
       <c r="P318">
-        <v>50.2</v>
+        <v>49.8</v>
       </c>
       <c r="Q318">
         <v>1.49</v>
@@ -24509,13 +24509,13 @@
         <v>135</v>
       </c>
       <c r="U318">
-        <v>50.2</v>
+        <v>49.8</v>
       </c>
       <c r="V318">
         <v>1.49</v>
       </c>
       <c r="W318">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X318">
         <v>0.89</v>
@@ -28068,16 +28068,16 @@
         <v>53</v>
       </c>
       <c r="D365">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E365">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F365">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G365">
-        <v>1427.55</v>
+        <v>1438.93</v>
       </c>
       <c r="H365">
         <v>160</v>
@@ -28089,7 +28089,7 @@
         <v>88</v>
       </c>
       <c r="K365">
-        <v>46.6</v>
+        <v>46.1</v>
       </c>
       <c r="L365">
         <v>2.79</v>
@@ -28104,7 +28104,7 @@
         <v>88</v>
       </c>
       <c r="P365">
-        <v>46.6</v>
+        <v>46.1</v>
       </c>
       <c r="Q365">
         <v>2.79</v>
@@ -28119,16 +28119,16 @@
         <v>88</v>
       </c>
       <c r="U365">
-        <v>46.6</v>
+        <v>46.1</v>
       </c>
       <c r="V365">
         <v>2.79</v>
       </c>
       <c r="W365">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="X365">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="Y365">
         <v>0.31</v>
@@ -32254,16 +32254,16 @@
         <v>53</v>
       </c>
       <c r="D421">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E421">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F421">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G421">
-        <v>28.2</v>
+        <v>22.56</v>
       </c>
       <c r="H421">
         <v>4</v>
@@ -32275,7 +32275,7 @@
         <v>3</v>
       </c>
       <c r="K421">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="L421">
         <v>0</v>
@@ -32290,7 +32290,7 @@
         <v>3</v>
       </c>
       <c r="P421">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="Q421">
         <v>0</v>
@@ -32305,7 +32305,7 @@
         <v>3</v>
       </c>
       <c r="U421">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="V421">
         <v>0</v>
@@ -32314,7 +32314,7 @@
         <v>0</v>
       </c>
       <c r="X421">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="Y421">
         <v>0</v>
@@ -33192,16 +33192,16 @@
         <v>53</v>
       </c>
       <c r="D434">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E434">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F434">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G434">
-        <v>259.44</v>
+        <v>265.08</v>
       </c>
       <c r="H434">
         <v>12</v>
@@ -33213,7 +33213,7 @@
         <v>11</v>
       </c>
       <c r="K434">
-        <v>24.4</v>
+        <v>23.9</v>
       </c>
       <c r="L434">
         <v>1.58</v>
@@ -33228,7 +33228,7 @@
         <v>11</v>
       </c>
       <c r="P434">
-        <v>24.4</v>
+        <v>23.9</v>
       </c>
       <c r="Q434">
         <v>1.58</v>
@@ -33243,13 +33243,13 @@
         <v>11</v>
       </c>
       <c r="U434">
-        <v>24.4</v>
+        <v>23.9</v>
       </c>
       <c r="V434">
         <v>1.58</v>
       </c>
       <c r="W434">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="X434">
         <v>0.26</v>
@@ -37936,16 +37936,16 @@
         <v>53</v>
       </c>
       <c r="D496">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E496">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F496">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G496">
-        <v>26.91</v>
+        <v>17.94</v>
       </c>
       <c r="H496">
         <v>1</v>
@@ -37957,7 +37957,7 @@
         <v>1</v>
       </c>
       <c r="K496">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="L496">
         <v>0</v>
@@ -37972,7 +37972,7 @@
         <v>1</v>
       </c>
       <c r="P496">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="Q496">
         <v>0</v>
@@ -37987,7 +37987,7 @@
         <v>1</v>
       </c>
       <c r="U496">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="V496">
         <v>0</v>
@@ -37996,7 +37996,7 @@
         <v>0</v>
       </c>
       <c r="X496">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="Y496">
         <v>0</v>
@@ -38232,16 +38232,16 @@
         <v>53</v>
       </c>
       <c r="D500">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E500">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F500">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G500">
-        <v>376.74</v>
+        <v>385.71</v>
       </c>
       <c r="H500">
         <v>18</v>
@@ -38253,7 +38253,7 @@
         <v>15</v>
       </c>
       <c r="K500">
-        <v>35.7</v>
+        <v>34.9</v>
       </c>
       <c r="L500">
         <v>0</v>
@@ -38268,7 +38268,7 @@
         <v>15</v>
       </c>
       <c r="P500">
-        <v>35.7</v>
+        <v>34.9</v>
       </c>
       <c r="Q500">
         <v>0</v>
@@ -38283,7 +38283,7 @@
         <v>15</v>
       </c>
       <c r="U500">
-        <v>35.7</v>
+        <v>34.9</v>
       </c>
       <c r="V500">
         <v>0</v>
@@ -38292,7 +38292,7 @@
         <v>0</v>
       </c>
       <c r="X500">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="Y500">
         <v>0</v>
@@ -45726,16 +45726,16 @@
         <v>53</v>
       </c>
       <c r="D602">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E602">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F602">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G602">
-        <v>25.84</v>
+        <v>13.82</v>
       </c>
       <c r="H602">
         <v>0</v>
@@ -45936,16 +45936,16 @@
         <v>53</v>
       </c>
       <c r="D605">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E605">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F605">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G605">
-        <v>337.14</v>
+        <v>344.05</v>
       </c>
       <c r="H605">
         <v>16</v>
@@ -45957,7 +45957,7 @@
         <v>14</v>
       </c>
       <c r="K605">
-        <v>25.9</v>
+        <v>25.5</v>
       </c>
       <c r="L605">
         <v>0.89</v>
@@ -45972,7 +45972,7 @@
         <v>14</v>
       </c>
       <c r="P605">
-        <v>25.9</v>
+        <v>25.5</v>
       </c>
       <c r="Q605">
         <v>0.89</v>
@@ -45987,7 +45987,7 @@
         <v>14</v>
       </c>
       <c r="U605">
-        <v>25.9</v>
+        <v>25.5</v>
       </c>
       <c r="V605">
         <v>0.89</v>
@@ -45996,7 +45996,7 @@
         <v>0.26</v>
       </c>
       <c r="X605">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="Y605">
         <v>0.04</v>
@@ -46244,16 +46244,16 @@
         <v>53</v>
       </c>
       <c r="D609">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E609">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F609">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G609">
-        <v>966.88</v>
+        <v>971.99</v>
       </c>
       <c r="H609">
         <v>109</v>
@@ -46265,7 +46265,7 @@
         <v>70</v>
       </c>
       <c r="K609">
-        <v>47.3</v>
+        <v>47</v>
       </c>
       <c r="L609">
         <v>1.33</v>
@@ -46280,7 +46280,7 @@
         <v>70</v>
       </c>
       <c r="P609">
-        <v>47.3</v>
+        <v>47</v>
       </c>
       <c r="Q609">
         <v>1.33</v>
@@ -46295,16 +46295,16 @@
         <v>70</v>
       </c>
       <c r="U609">
-        <v>47.3</v>
+        <v>47</v>
       </c>
       <c r="V609">
         <v>1.33</v>
       </c>
       <c r="W609">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="X609">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="Y609">
         <v>0.15</v>
@@ -50907,16 +50907,16 @@
         <v>53</v>
       </c>
       <c r="D671">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E671">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F671">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G671">
-        <v>19.59</v>
+        <v>13.06</v>
       </c>
       <c r="H671">
         <v>1</v>
@@ -50928,7 +50928,7 @@
         <v>1</v>
       </c>
       <c r="K671">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="L671">
         <v>0</v>
@@ -50943,7 +50943,7 @@
         <v>1</v>
       </c>
       <c r="P671">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="Q671">
         <v>0</v>
@@ -50958,7 +50958,7 @@
         <v>1</v>
       </c>
       <c r="U671">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="V671">
         <v>0</v>
@@ -50967,7 +50967,7 @@
         <v>0</v>
       </c>
       <c r="X671">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="Y671">
         <v>0</v>
@@ -51780,16 +51780,16 @@
         <v>53</v>
       </c>
       <c r="D683">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E683">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F683">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G683">
-        <v>215.49</v>
+        <v>222.02</v>
       </c>
       <c r="H683">
         <v>7</v>
@@ -51801,7 +51801,7 @@
         <v>7</v>
       </c>
       <c r="K683">
-        <v>21.2</v>
+        <v>20.6</v>
       </c>
       <c r="L683">
         <v>5.57</v>
@@ -51816,7 +51816,7 @@
         <v>7</v>
       </c>
       <c r="P683">
-        <v>21.2</v>
+        <v>20.6</v>
       </c>
       <c r="Q683">
         <v>5.57</v>
@@ -51831,13 +51831,13 @@
         <v>7</v>
       </c>
       <c r="U683">
-        <v>21.2</v>
+        <v>20.6</v>
       </c>
       <c r="V683">
         <v>5.57</v>
       </c>
       <c r="W683">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X683">
         <v>0.21</v>
